--- a/news_daily/2026-09-19.xlsx
+++ b/news_daily/2026-09-19.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,17 +57,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE0B2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFCDD2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,10 +94,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH7"/>
+  <dimension ref="A1:BL7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -534,6 +534,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -837,6 +841,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -872,28 +896,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>監管調查</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -933,7 +961,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>REGULATORY_INVESTIGATION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -942,7 +970,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>ae5ccd2e4b184cd1826666788415e2a1</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>0f357b264bfa139d7ca699d1</t>
@@ -963,7 +995,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -999,843 +1035,919 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>FTNT</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Fortinet, Inc.</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-09-19T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Fortinet (FTNT) Stock Could Be 22% Overvalued On New York Hub Opening</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>估值疑慮</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>0.701</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQS09HemlWSTNEamhmNE9iOUFveWpwdGV4MUZ1S21MalR1Nmd4RmxiNVkxdGt0MFpRZ2tMT2VwN1RJQWJnTnVaT3A1ejZMOWNFTjRaVjVodjQ2U2hEaFJhU3gtYnhOeVlyWGFQSXFKLVNROHltb0lyenB6cEpNaXlmR2RfVWJuSFc1U09CbEQ0aGtQTTgwZkJqSg?oc=5</t>
         </is>
       </c>
-      <c r="V3" s="3" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="Y3" s="2" t="inlineStr">
         <is>
           <t>VALUATION_CONCERN</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>overvalued</t>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>6ac00548245445748a90a56c</t>
         </is>
       </c>
-      <c r="AD3" s="3" t="inlineStr">
+      <c r="AD3" s="2" t="inlineStr">
         <is>
           <t>7286f4287c236e712269f7c7</t>
         </is>
       </c>
-      <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AG3" s="2" t="inlineStr"/>
+      <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AK3" s="2" t="inlineStr"/>
+      <c r="AL3" s="2" t="inlineStr"/>
+      <c r="AM3" s="2" t="inlineStr"/>
+      <c r="AN3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AP3" s="2" t="inlineStr"/>
+      <c r="AQ3" s="2" t="inlineStr"/>
+      <c r="AR3" s="2" t="inlineStr"/>
+      <c r="AS3" s="2" t="inlineStr"/>
+      <c r="AT3" s="2" t="inlineStr"/>
+      <c r="AU3" s="2" t="inlineStr"/>
+      <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
+      <c r="AX3" s="2" t="inlineStr"/>
+      <c r="AY3" s="2" t="inlineStr"/>
+      <c r="AZ3" s="2" t="inlineStr"/>
+      <c r="BA3" s="2" t="inlineStr"/>
+      <c r="BB3" s="2" t="inlineStr">
         <is>
           <t>FTNT</t>
         </is>
       </c>
-      <c r="BC3" s="3" t="inlineStr">
+      <c r="BC3" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="3" t="inlineStr"/>
-      <c r="BE3" s="3" t="inlineStr">
+      <c r="BD3" s="2" t="inlineStr"/>
+      <c r="BE3" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF3" s="3" t="inlineStr">
+      <c r="BF3" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG3" s="3" t="inlineStr">
+      <c r="BG3" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>LEN</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Lennar Corporation Class A Common Stock</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>2026-09-19T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Lennar’s Earnings Miss May Be Sending a Bigger Warning About U.S. Housing</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>財報不如預期</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>'-0.921</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>原始代號與公司名稱交叉核對</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNcEZXQ3RsLUtTR0EwQWdEazVOWHlVT1dIYVVIMFJ5RHkyc19kUzhvZVVsRUV3dVZuSGdVT2lpRlZwNW9za2RkTGVTVjhiZWNzRERReG1GV2ZIQldQd0dJYUthTkFMNTZVejNjRi14cFRnUzA4Mi10STRXVUFyNHh6Q2lXRWRndXV1WFhIS2s0SWJOdEM5a05oOUNB?oc=5</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>FINANCIAL</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>EARNINGS_MISS</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>earnings miss</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>5b8a2aa589f07d1310957815</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr">
         <is>
           <t>35c2f650041aceb96195e59f</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr">
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="3" t="inlineStr">
         <is>
           <t>LEN</t>
         </is>
       </c>
-      <c r="BC4" s="4" t="inlineStr">
+      <c r="BC4" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="4" t="inlineStr"/>
-      <c r="BE4" s="4" t="inlineStr">
+      <c r="BD4" s="3" t="inlineStr"/>
+      <c r="BE4" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF4" s="4" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG4" s="4" t="inlineStr">
+      <c r="BG4" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr"/>
+      <c r="BL4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>EXPD</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Expeditors International</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>2026-09-19T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Expeditors International Of Washington (EXPD) Stock Could Be 12% Overvalued On Cash Flow</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>估值疑慮</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>'-0.354</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPNmJYQ1gwWm1iQVlhVVBzUkZFU29IbzRBMkFLYXJHZm1IRU1lTWo2LVVSdTY4aU9oeHgxVUIwQmVISVp2RGpoNUEzeFItc2xzeXhLMXc0TG5odnhqekhrTlRwMEFMRm9mWEpiNGx0Qmczai13c2V6eXQ3aEMxSEJ0Z0c0WmktY0hzSFQzWFRmaHQ5LVJ0Qks0Tk10MU5IcndxNW50UGU1ZlVKd3EzUTkyeg?oc=5</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>VALUATION_CONCERN</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>overvalued</t>
         </is>
       </c>
-      <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="3" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>dd5df62611560ee706ece310</t>
         </is>
       </c>
-      <c r="AD5" s="3" t="inlineStr">
+      <c r="AD5" s="2" t="inlineStr">
         <is>
           <t>3b965275ae28738e43876639</t>
         </is>
       </c>
-      <c r="AE5" s="3" t="inlineStr"/>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr"/>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AK5" s="2" t="inlineStr"/>
+      <c r="AL5" s="2" t="inlineStr"/>
+      <c r="AM5" s="2" t="inlineStr"/>
+      <c r="AN5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AP5" s="2" t="inlineStr"/>
+      <c r="AQ5" s="2" t="inlineStr"/>
+      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AS5" s="2" t="inlineStr"/>
+      <c r="AT5" s="2" t="inlineStr"/>
+      <c r="AU5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" s="2" t="inlineStr"/>
+      <c r="AX5" s="2" t="inlineStr"/>
+      <c r="AY5" s="2" t="inlineStr"/>
+      <c r="AZ5" s="2" t="inlineStr"/>
+      <c r="BA5" s="2" t="inlineStr"/>
+      <c r="BB5" s="2" t="inlineStr">
         <is>
           <t>EXPD</t>
         </is>
       </c>
-      <c r="BC5" s="3" t="inlineStr">
+      <c r="BC5" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="3" t="inlineStr"/>
-      <c r="BE5" s="3" t="inlineStr">
+      <c r="BD5" s="2" t="inlineStr"/>
+      <c r="BE5" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF5" s="3" t="inlineStr"/>
-      <c r="BG5" s="3" t="inlineStr">
+      <c r="BF5" s="2" t="inlineStr"/>
+      <c r="BG5" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>CVS</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>CVS Health Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>2026-09-19T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>$949 million fraud verdict costs CVS a business in Chapter 11</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>破產</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>'-0.917</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQNjRSZG1EOWpHRXdCV3EyVkh2eGI1S3F3WlpCc0J4MU9pZEhfcmlEaG9SX1pxd0p6VlppRy12RmJuR3RGR1h6dGlGbEdSWE5YWldFaFJUMl85bGgxcnQ3cTBYY0NNeEVHUFN3MWlDVEZfZjZXeDdicnRVYjJGOV9TeGwtUmQ2TmMwVzhGVVF1a3hHeWFHUVJKdnZn?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>BANKRUPTCY</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>chapter 11</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>46e25b0b36554b08bbc92c969b73a51e</t>
+        </is>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>7587592231bf590fdf0dd277</t>
+        </is>
+      </c>
+      <c r="AD6" s="4" t="inlineStr">
+        <is>
+          <t>239c8ebf393be1c5a12d1676</t>
+        </is>
+      </c>
+      <c r="AE6" s="4" t="inlineStr"/>
+      <c r="AF6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>'-0.917</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQNjRSZG1EOWpHRXdCV3EyVkh2eGI1S3F3WlpCc0J4MU9pZEhfcmlEaG9SX1pxd0p6VlppRy12RmJuR3RGR1h6dGlGbEdSWE5YWldFaFJUMl85bGgxcnQ3cTBYY0NNeEVHUFN3MWlDVEZfZjZXeDdicnRVYjJGOV9TeGwtUmQ2TmMwVzhGVVF1a3hHeWFHUVJKdnZn?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="5" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W6" s="5" t="inlineStr"/>
-      <c r="X6" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="5" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z6" s="5" t="inlineStr">
-        <is>
-          <t>chapter 11</t>
-        </is>
-      </c>
-      <c r="AA6" s="5" t="inlineStr"/>
-      <c r="AB6" s="5" t="inlineStr"/>
-      <c r="AC6" s="5" t="inlineStr">
-        <is>
-          <t>7587592231bf590fdf0dd277</t>
-        </is>
-      </c>
-      <c r="AD6" s="5" t="inlineStr">
-        <is>
-          <t>239c8ebf393be1c5a12d1676</t>
-        </is>
-      </c>
-      <c r="AE6" s="5" t="inlineStr"/>
-      <c r="AF6" s="5" t="inlineStr"/>
-      <c r="AG6" s="5" t="inlineStr"/>
-      <c r="AH6" s="5" t="inlineStr"/>
-      <c r="AI6" s="5" t="inlineStr"/>
-      <c r="AJ6" s="5" t="inlineStr"/>
-      <c r="AK6" s="5" t="inlineStr"/>
-      <c r="AL6" s="5" t="inlineStr"/>
-      <c r="AM6" s="5" t="inlineStr"/>
-      <c r="AN6" s="5" t="inlineStr"/>
-      <c r="AO6" s="5" t="inlineStr"/>
-      <c r="AP6" s="5" t="inlineStr"/>
-      <c r="AQ6" s="5" t="inlineStr"/>
-      <c r="AR6" s="5" t="inlineStr"/>
-      <c r="AS6" s="5" t="inlineStr"/>
-      <c r="AT6" s="5" t="inlineStr"/>
-      <c r="AU6" s="5" t="inlineStr"/>
-      <c r="AV6" s="5" t="inlineStr"/>
-      <c r="AW6" s="5" t="inlineStr">
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AS6" s="4" t="inlineStr"/>
+      <c r="AT6" s="4" t="inlineStr"/>
+      <c r="AU6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AW6" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX6" s="5" t="inlineStr"/>
-      <c r="AY6" s="5" t="inlineStr"/>
-      <c r="AZ6" s="5" t="inlineStr"/>
-      <c r="BA6" s="5" t="inlineStr"/>
-      <c r="BB6" s="5" t="inlineStr">
+      <c r="AX6" s="4" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr"/>
+      <c r="AZ6" s="4" t="inlineStr"/>
+      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BB6" s="4" t="inlineStr">
         <is>
           <t>CVS</t>
         </is>
       </c>
-      <c r="BC6" s="5" t="inlineStr">
+      <c r="BC6" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="5" t="inlineStr"/>
-      <c r="BE6" s="5" t="inlineStr">
+      <c r="BD6" s="4" t="inlineStr"/>
+      <c r="BE6" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="5" t="inlineStr">
+      <c r="BF6" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="5" t="inlineStr">
+      <c r="BG6" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="5" t="inlineStr"/>
+      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Kroger</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026-09-19T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Kroger (KR) Draws Tougher Antitrust Review For Its Planned Grocery Deal</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>反壟斷調查</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>'-0.865</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQelVPY2JtbFBBLU1DUzVwaTF3SjMyY0ItY3hKYjUyVGhlRVlxb2Z6Nkw1N2E4Y01hZkVqYUhrdXMtbzNVM0JKNnRsRTJ6SHBtYUlLQ1lkcUdERDZZc015R0ZVdmxlOEJsVHp3OWlhajRNbmljcUdaQWdTcGFvbTdsZWZjeFZlZldtWDV5M0lsd1JCUUpqZzBBS2QzVzRwT1U?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr"/>
+      <c r="X7" s="5" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y7" s="5" t="inlineStr">
+        <is>
+          <t>ANTITRUST_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z7" s="5" t="inlineStr">
+        <is>
+          <t>antitrust</t>
+        </is>
+      </c>
+      <c r="AA7" s="5" t="inlineStr"/>
+      <c r="AB7" s="5" t="inlineStr">
+        <is>
+          <t>1844d31855a6484dbb3278090d8b9188</t>
+        </is>
+      </c>
+      <c r="AC7" s="5" t="inlineStr">
+        <is>
+          <t>011644c35832d23a12514cc5</t>
+        </is>
+      </c>
+      <c r="AD7" s="5" t="inlineStr">
+        <is>
+          <t>bdabe3b050d6678ef0d7966e</t>
+        </is>
+      </c>
+      <c r="AE7" s="5" t="inlineStr"/>
+      <c r="AF7" s="5" t="inlineStr"/>
+      <c r="AG7" s="5" t="inlineStr"/>
+      <c r="AH7" s="5" t="inlineStr"/>
+      <c r="AI7" s="5" t="inlineStr"/>
+      <c r="AJ7" s="5" t="inlineStr"/>
+      <c r="AK7" s="5" t="inlineStr"/>
+      <c r="AL7" s="5" t="inlineStr"/>
+      <c r="AM7" s="5" t="inlineStr"/>
+      <c r="AN7" s="5" t="inlineStr"/>
+      <c r="AO7" s="5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>'-0.865</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQelVPY2JtbFBBLU1DUzVwaTF3SjMyY0ItY3hKYjUyVGhlRVlxb2Z6Nkw1N2E4Y01hZkVqYUhrdXMtbzNVM0JKNnRsRTJ6SHBtYUlLQ1lkcUdERDZZc015R0ZVdmxlOEJsVHp3OWlhajRNbmljcUdaQWdTcGFvbTdsZWZjeFZlZldtWDV5M0lsd1JCUUpqZzBBS2QzVzRwT1U?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t>antitrust</t>
-        </is>
-      </c>
-      <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
-      <c r="AC7" s="2" t="inlineStr">
-        <is>
-          <t>011644c35832d23a12514cc5</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="inlineStr">
-        <is>
-          <t>bdabe3b050d6678ef0d7966e</t>
-        </is>
-      </c>
-      <c r="AE7" s="2" t="inlineStr"/>
-      <c r="AF7" s="2" t="inlineStr"/>
-      <c r="AG7" s="2" t="inlineStr"/>
-      <c r="AH7" s="2" t="inlineStr"/>
-      <c r="AI7" s="2" t="inlineStr"/>
-      <c r="AJ7" s="2" t="inlineStr"/>
-      <c r="AK7" s="2" t="inlineStr"/>
-      <c r="AL7" s="2" t="inlineStr"/>
-      <c r="AM7" s="2" t="inlineStr"/>
-      <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
-      <c r="AP7" s="2" t="inlineStr"/>
-      <c r="AQ7" s="2" t="inlineStr"/>
-      <c r="AR7" s="2" t="inlineStr"/>
-      <c r="AS7" s="2" t="inlineStr"/>
-      <c r="AT7" s="2" t="inlineStr"/>
-      <c r="AU7" s="2" t="inlineStr"/>
-      <c r="AV7" s="2" t="inlineStr"/>
-      <c r="AW7" s="2" t="inlineStr"/>
-      <c r="AX7" s="2" t="inlineStr"/>
-      <c r="AY7" s="2" t="inlineStr"/>
-      <c r="AZ7" s="2" t="inlineStr"/>
-      <c r="BA7" s="2" t="inlineStr"/>
-      <c r="BB7" s="2" t="inlineStr">
+      <c r="AP7" s="5" t="inlineStr"/>
+      <c r="AQ7" s="5" t="inlineStr"/>
+      <c r="AR7" s="5" t="inlineStr"/>
+      <c r="AS7" s="5" t="inlineStr"/>
+      <c r="AT7" s="5" t="inlineStr"/>
+      <c r="AU7" s="5" t="inlineStr"/>
+      <c r="AV7" s="5" t="inlineStr"/>
+      <c r="AW7" s="5" t="inlineStr"/>
+      <c r="AX7" s="5" t="inlineStr"/>
+      <c r="AY7" s="5" t="inlineStr"/>
+      <c r="AZ7" s="5" t="inlineStr"/>
+      <c r="BA7" s="5" t="inlineStr"/>
+      <c r="BB7" s="5" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="BC7" s="2" t="inlineStr">
+      <c r="BC7" s="5" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="2" t="inlineStr"/>
-      <c r="BE7" s="2" t="inlineStr">
+      <c r="BD7" s="5" t="inlineStr"/>
+      <c r="BE7" s="5" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF7" s="2" t="inlineStr"/>
-      <c r="BG7" s="2" t="inlineStr">
+      <c r="BF7" s="5" t="inlineStr"/>
+      <c r="BG7" s="5" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BH7" s="5" t="inlineStr"/>
+      <c r="BI7" s="5" t="inlineStr"/>
+      <c r="BJ7" s="5" t="inlineStr"/>
+      <c r="BK7" s="5" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH7"/>
+  <autoFilter ref="A1:BL7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1846,7 +1958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BL4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1909,6 +2021,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2212,168 +2328,200 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>LEN</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Lennar Corporation Class A Common Stock</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>2026-09-19T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Coinbase Files With CFTC To List US Single-Stock Perpetual Futures, Including AAPL And TSLA Contracts</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Lennar’s Earnings Miss May Be Sending a Bigger Warning About U.S. Housing</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>財報不如預期</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>'-0.02</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObFQ2MVVNYklFWnVXcW1vM3lEQndhYkFwUzJpUWtTeUN5RWIxUzlGWnkyTmNDYV9mbWZzNDFXYnlyMkVTMHlZcld2d1MwQzJCRUw3WUE3ZDVjZV84UTU5Zm9uQmo1RzBSbmo0Vm9rNFhwbENxeXlVa3IwRmJ0SUxPcUlzbFNlY1hCdGtpWjhGUE1nelJKNWFfSQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>'-0.921</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>原始代號與公司名稱交叉核對</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNcEZXQ3RsLUtTR0EwQWdEazVOWHlVT1dIYVVIMFJ5RHkyc19kUzhvZVVsRUV3dVZuSGdVT2lpRlZwNW9za2RkTGVTVjhiZWNzRERReG1GV2ZIQldQd0dJYUthTkFMNTZVejNjRi14cFRnUzA4Mi10STRXVUFyNHh6Q2lXRWRndXV1WFhIS2s0SWJOdEM5a05oOUNB?oc=5</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>CFTC；FTC</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>0f357b264bfa139d7ca699d1</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>83aef3fa88f62dc450eaa09f</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr"/>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>EARNINGS_MISS</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>earnings miss</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>5b8a2aa589f07d1310957815</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>35c2f650041aceb96195e59f</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr"/>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" s="3" t="inlineStr"/>
+      <c r="AI2" s="3" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" s="3" t="inlineStr"/>
+      <c r="AM2" s="3" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AP2" s="3" t="inlineStr"/>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr"/>
+      <c r="AS2" s="3" t="inlineStr"/>
+      <c r="AT2" s="3" t="inlineStr"/>
+      <c r="AU2" s="3" t="inlineStr"/>
+      <c r="AV2" s="3" t="inlineStr"/>
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX2" s="3" t="inlineStr"/>
+      <c r="AY2" s="3" t="inlineStr"/>
+      <c r="AZ2" s="3" t="inlineStr"/>
+      <c r="BA2" s="3" t="inlineStr"/>
+      <c r="BB2" s="3" t="inlineStr">
+        <is>
+          <t>LEN</t>
+        </is>
+      </c>
+      <c r="BC2" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD2" s="2" t="inlineStr"/>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr"/>
-      <c r="BG2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BD2" s="3" t="inlineStr"/>
+      <c r="BE2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG2" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr"/>
+      <c r="BL2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2388,12 +2536,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>LEN</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Lennar Corporation Class A Common Stock</t>
+          <t>CVS Health Corporation Common Stock</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -2403,34 +2551,38 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Lennar’s Earnings Miss May Be Sending a Bigger Warning About U.S. Housing</t>
+          <t>$949 million fraud verdict costs CVS a business in Chapter 11</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>財報不如預期</t>
+          <t>破產</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -2440,7 +2592,7 @@
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>'-0.921</t>
+          <t>'-0.917</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr"/>
@@ -2449,12 +2601,12 @@
       <c r="S3" s="4" t="inlineStr"/>
       <c r="T3" s="4" t="inlineStr">
         <is>
-          <t>原始代號與公司名稱交叉核對</t>
+          <t>公司清單／別名核對</t>
         </is>
       </c>
       <c r="U3" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNcEZXQ3RsLUtTR0EwQWdEazVOWHlVT1dIYVVIMFJ5RHkyc19kUzhvZVVsRUV3dVZuSGdVT2lpRlZwNW9za2RkTGVTVjhiZWNzRERReG1GV2ZIQldQd0dJYUthTkFMNTZVejNjRi14cFRnUzA4Mi10STRXVUFyNHh6Q2lXRWRndXV1WFhIS2s0SWJOdEM5a05oOUNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQNjRSZG1EOWpHRXdCV3EyVkh2eGI1S3F3WlpCc0J4MU9pZEhfcmlEaG9SX1pxd0p6VlppRy12RmJuR3RGR1h6dGlGbEdSWE5YWldFaFJUMl85bGgxcnQ3cTBYY0NNeEVHUFN3MWlDVEZfZjZXeDdicnRVYjJGOV9TeGwtUmQ2TmMwVzhGVVF1a3hHeWFHUVJKdnZn?oc=5</t>
         </is>
       </c>
       <c r="V3" s="4" t="inlineStr">
@@ -2470,24 +2622,28 @@
       </c>
       <c r="Y3" s="4" t="inlineStr">
         <is>
-          <t>EARNINGS_MISS</t>
+          <t>BANKRUPTCY</t>
         </is>
       </c>
       <c r="Z3" s="4" t="inlineStr">
         <is>
-          <t>earnings miss</t>
+          <t>chapter 11</t>
         </is>
       </c>
       <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>46e25b0b36554b08bbc92c969b73a51e</t>
+        </is>
+      </c>
       <c r="AC3" s="4" t="inlineStr">
         <is>
-          <t>5b8a2aa589f07d1310957815</t>
+          <t>7587592231bf590fdf0dd277</t>
         </is>
       </c>
       <c r="AD3" s="4" t="inlineStr">
         <is>
-          <t>35c2f650041aceb96195e59f</t>
+          <t>239c8ebf393be1c5a12d1676</t>
         </is>
       </c>
       <c r="AE3" s="4" t="inlineStr"/>
@@ -2500,7 +2656,11 @@
       <c r="AL3" s="4" t="inlineStr"/>
       <c r="AM3" s="4" t="inlineStr"/>
       <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="4" t="inlineStr"/>
       <c r="AQ3" s="4" t="inlineStr"/>
       <c r="AR3" s="4" t="inlineStr"/>
@@ -2519,7 +2679,7 @@
       <c r="BA3" s="4" t="inlineStr"/>
       <c r="BB3" s="4" t="inlineStr">
         <is>
-          <t>LEN</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="BC3" s="4" t="inlineStr">
@@ -2544,6 +2704,18 @@
         </is>
       </c>
       <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BI3" s="4" t="inlineStr"/>
+      <c r="BJ3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -2558,12 +2730,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>CVS Health Corporation Common Stock</t>
+          <t>Kroger</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -2573,18 +2745,18 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>$949 million fraud verdict costs CVS a business in Chapter 11</t>
+          <t>Kroger (KR) Draws Tougher Antitrust Review For Its Planned Grocery Deal</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>破產</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -2594,13 +2766,17 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
@@ -2610,7 +2786,7 @@
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>'-0.917</t>
+          <t>'-0.865</t>
         </is>
       </c>
       <c r="P4" s="5" t="inlineStr"/>
@@ -2624,7 +2800,7 @@
       </c>
       <c r="U4" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQNjRSZG1EOWpHRXdCV3EyVkh2eGI1S3F3WlpCc0J4MU9pZEhfcmlEaG9SX1pxd0p6VlppRy12RmJuR3RGR1h6dGlGbEdSWE5YWldFaFJUMl85bGgxcnQ3cTBYY0NNeEVHUFN3MWlDVEZfZjZXeDdicnRVYjJGOV9TeGwtUmQ2TmMwVzhGVVF1a3hHeWFHUVJKdnZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQelVPY2JtbFBBLU1DUzVwaTF3SjMyY0ItY3hKYjUyVGhlRVlxb2Z6Nkw1N2E4Y01hZkVqYUhrdXMtbzNVM0JKNnRsRTJ6SHBtYUlLQ1lkcUdERDZZc015R0ZVdmxlOEJsVHp3OWlhajRNbmljcUdaQWdTcGFvbTdsZWZjeFZlZldtWDV5M0lsd1JCUUpqZzBBS2QzVzRwT1U?oc=5</t>
         </is>
       </c>
       <c r="V4" s="5" t="inlineStr">
@@ -2635,29 +2811,33 @@
       <c r="W4" s="5" t="inlineStr"/>
       <c r="X4" s="5" t="inlineStr">
         <is>
-          <t>FINANCIAL</t>
+          <t>LEGAL</t>
         </is>
       </c>
       <c r="Y4" s="5" t="inlineStr">
         <is>
-          <t>BANKRUPTCY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z4" s="5" t="inlineStr">
         <is>
-          <t>chapter 11</t>
+          <t>antitrust</t>
         </is>
       </c>
       <c r="AA4" s="5" t="inlineStr"/>
-      <c r="AB4" s="5" t="inlineStr"/>
+      <c r="AB4" s="5" t="inlineStr">
+        <is>
+          <t>1844d31855a6484dbb3278090d8b9188</t>
+        </is>
+      </c>
       <c r="AC4" s="5" t="inlineStr">
         <is>
-          <t>7587592231bf590fdf0dd277</t>
+          <t>011644c35832d23a12514cc5</t>
         </is>
       </c>
       <c r="AD4" s="5" t="inlineStr">
         <is>
-          <t>239c8ebf393be1c5a12d1676</t>
+          <t>bdabe3b050d6678ef0d7966e</t>
         </is>
       </c>
       <c r="AE4" s="5" t="inlineStr"/>
@@ -2670,7 +2850,11 @@
       <c r="AL4" s="5" t="inlineStr"/>
       <c r="AM4" s="5" t="inlineStr"/>
       <c r="AN4" s="5" t="inlineStr"/>
-      <c r="AO4" s="5" t="inlineStr"/>
+      <c r="AO4" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="5" t="inlineStr"/>
       <c r="AQ4" s="5" t="inlineStr"/>
       <c r="AR4" s="5" t="inlineStr"/>
@@ -2678,18 +2862,14 @@
       <c r="AT4" s="5" t="inlineStr"/>
       <c r="AU4" s="5" t="inlineStr"/>
       <c r="AV4" s="5" t="inlineStr"/>
-      <c r="AW4" s="5" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW4" s="5" t="inlineStr"/>
       <c r="AX4" s="5" t="inlineStr"/>
       <c r="AY4" s="5" t="inlineStr"/>
       <c r="AZ4" s="5" t="inlineStr"/>
       <c r="BA4" s="5" t="inlineStr"/>
       <c r="BB4" s="5" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="BC4" s="5" t="inlineStr">
@@ -2700,185 +2880,31 @@
       <c r="BD4" s="5" t="inlineStr"/>
       <c r="BE4" s="5" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF4" s="5" t="inlineStr"/>
       <c r="BG4" s="5" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Kroger</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-19T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Kroger (KR) Draws Tougher Antitrust Review For Its Planned Grocery Deal</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>'-0.865</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQelVPY2JtbFBBLU1DUzVwaTF3SjMyY0ItY3hKYjUyVGhlRVlxb2Z6Nkw1N2E4Y01hZkVqYUhrdXMtbzNVM0JKNnRsRTJ6SHBtYUlLQ1lkcUdERDZZc015R0ZVdmxlOEJsVHp3OWlhajRNbmljcUdaQWdTcGFvbTdsZWZjeFZlZldtWDV5M0lsd1JCUUpqZzBBS2QzVzRwT1U?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>antitrust</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>011644c35832d23a12514cc5</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>bdabe3b050d6678ef0d7966e</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
-      <c r="AG5" s="2" t="inlineStr"/>
-      <c r="AH5" s="2" t="inlineStr"/>
-      <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr"/>
-      <c r="AK5" s="2" t="inlineStr"/>
-      <c r="AL5" s="2" t="inlineStr"/>
-      <c r="AM5" s="2" t="inlineStr"/>
-      <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
-      <c r="AP5" s="2" t="inlineStr"/>
-      <c r="AQ5" s="2" t="inlineStr"/>
-      <c r="AR5" s="2" t="inlineStr"/>
-      <c r="AS5" s="2" t="inlineStr"/>
-      <c r="AT5" s="2" t="inlineStr"/>
-      <c r="AU5" s="2" t="inlineStr"/>
-      <c r="AV5" s="2" t="inlineStr"/>
-      <c r="AW5" s="2" t="inlineStr"/>
-      <c r="AX5" s="2" t="inlineStr"/>
-      <c r="AY5" s="2" t="inlineStr"/>
-      <c r="AZ5" s="2" t="inlineStr"/>
-      <c r="BA5" s="2" t="inlineStr"/>
-      <c r="BB5" s="2" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="BC5" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD5" s="2" t="inlineStr"/>
-      <c r="BE5" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF5" s="2" t="inlineStr"/>
-      <c r="BG5" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI4" s="5" t="inlineStr"/>
+      <c r="BJ4" s="5" t="inlineStr"/>
+      <c r="BK4" s="5" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH5"/>
+  <autoFilter ref="A1:BL4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2889,7 +2915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2952,6 +2978,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3255,9 +3285,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3268,7 +3318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3331,6 +3381,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3634,9 +3688,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3647,7 +3721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3697,477 +3771,768 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>ticker-audit-20261024-081549</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>ticker-audit</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>daily-2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="3" t="n">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="3" t="inlineStr"/>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr"/>
-      <c r="V2" s="3" t="inlineStr"/>
-      <c r="W2" s="3" t="inlineStr"/>
-      <c r="X2" s="3" t="inlineStr"/>
-      <c r="Y2" s="3" t="inlineStr"/>
-      <c r="Z2" s="3" t="inlineStr"/>
-      <c r="AA2" s="3" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>daily-2026-10-25</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="b">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Q3" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="R3" s="3" t="n">
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>2089</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="n">
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="Z3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="V3" s="2" t="n">
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>daily-2026-10-24</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="n">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>3802</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ticker-audit-20261024-081549</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ticker-audit</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:11.949238+08:00</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:18.833437+08:00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="n">
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="n">
+      <c r="M8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="b">
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="R5" s="3" t="n">
+      <c r="V8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="3" t="n">
+      <c r="W8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-09-19.xlsx
+++ b/news_daily/2026-09-19.xlsx
@@ -1275,13 +1275,17 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -1330,7 +1334,11 @@
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>5745ba12aa38489b9ef1404c93db9a8d</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>5b8a2aa589f07d1310957815</t>
@@ -1351,7 +1359,11 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
@@ -1397,8 +1409,16 @@
       <c r="BH4" s="3" t="inlineStr"/>
       <c r="BI4" s="3" t="inlineStr"/>
       <c r="BJ4" s="3" t="inlineStr"/>
-      <c r="BK4" s="3" t="inlineStr"/>
-      <c r="BL4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2398,13 +2418,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -2453,7 +2477,11 @@
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr"/>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>5745ba12aa38489b9ef1404c93db9a8d</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>5b8a2aa589f07d1310957815</t>
@@ -2474,7 +2502,11 @@
       <c r="AL2" s="3" t="inlineStr"/>
       <c r="AM2" s="3" t="inlineStr"/>
       <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="3" t="inlineStr"/>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr"/>
@@ -2520,8 +2552,16 @@
       <c r="BH2" s="3" t="inlineStr"/>
       <c r="BI2" s="3" t="inlineStr"/>
       <c r="BJ2" s="3" t="inlineStr"/>
-      <c r="BK2" s="3" t="inlineStr"/>
-      <c r="BL2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">

--- a/news_daily/2026-09-19.xlsx
+++ b/news_daily/2026-09-19.xlsx
@@ -1086,28 +1086,32 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1147,7 +1151,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -1156,7 +1160,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>a4959ff915764717b76ab042d0b839e7</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>6ac00548245445748a90a56c</t>
@@ -1177,7 +1185,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1221,10 +1233,22 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1454,28 +1478,32 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1515,7 +1543,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1524,7 +1552,11 @@
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>9ecdd9c4b925426f8bfe5a7026757f4b</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>dd5df62611560ee706ece310</t>
@@ -1545,7 +1577,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1581,10 +1617,22 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
